--- a/artfynd/A 57119-2025 artfynd.xlsx
+++ b/artfynd/A 57119-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130016681</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57119-2025 artfynd.xlsx
+++ b/artfynd/A 57119-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130016681</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57119-2025 artfynd.xlsx
+++ b/artfynd/A 57119-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1156,6 +1156,489 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130238708</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98833</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björnmyrbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>367309</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6610563</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på en yta av ca 15m^2</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Petter Brorson Edh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Petter Brorson Edh</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130238763</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98833</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björnmyrbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>367391</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6610613</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Petter Brorson Edh</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Petter Brorson Edh</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130238755</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björnmyrbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>367329</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6610576</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Petter Brorson Edh</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Petter Brorson Edh</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130238760</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8440</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björnmyrbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>367325</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6610581</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Petter Brorson Edh</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Petter Brorson Edh</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57119-2025 artfynd.xlsx
+++ b/artfynd/A 57119-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130016681</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>130124803</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>130124199</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57119-2025 artfynd.xlsx
+++ b/artfynd/A 57119-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130016681</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>130124803</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,60 +916,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130124199</v>
+        <v>130123722</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnmyrbäcken, Björnmyrbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>367331</v>
+        <v>367260</v>
       </c>
       <c r="R4" t="n">
-        <v>6610578</v>
+        <v>6610593</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca 200 st på en yta av 4×4 m. Såg några här o var i området. 3 st gamla blomställningar.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,14 +1010,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1039,60 +1021,67 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jesper Granback, Petter Brorson Edh</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130123722</v>
+        <v>130124199</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnmyrbäcken, Björnmyrbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>367260</v>
+        <v>367331</v>
       </c>
       <c r="R5" t="n">
-        <v>6610593</v>
+        <v>6610578</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca 200 st på en yta av 4×4 m. Såg några här o var i området. 3 st gamla blomställningar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,8 +1134,14 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jesper Granback, Petter Brorson Edh</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1161,7 +1161,7 @@
         <v>130238708</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>130238763</v>
       </c>
       <c r="B7" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57119-2025 artfynd.xlsx
+++ b/artfynd/A 57119-2025 artfynd.xlsx
@@ -916,53 +916,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130123722</v>
+        <v>130124199</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnmyrbäcken, Björnmyrbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>367260</v>
+        <v>367331</v>
       </c>
       <c r="R4" t="n">
-        <v>6610593</v>
+        <v>6610578</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca 200 st på en yta av 4×4 m. Såg några här o var i området. 3 st gamla blomställningar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,8 +1022,14 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1021,67 +1039,60 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jesper Granback, Petter Brorson Edh</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130124199</v>
+        <v>130123722</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnmyrbäcken, Björnmyrbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>367331</v>
+        <v>367260</v>
       </c>
       <c r="R5" t="n">
-        <v>6610578</v>
+        <v>6610593</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca 200 st på en yta av 4×4 m. Såg några här o var i området. 3 st gamla blomställningar.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,14 +1140,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jesper Granback, Petter Brorson Edh</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 57119-2025 artfynd.xlsx
+++ b/artfynd/A 57119-2025 artfynd.xlsx
@@ -916,60 +916,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130124199</v>
+        <v>130123722</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnmyrbäcken, Björnmyrbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>367331</v>
+        <v>367260</v>
       </c>
       <c r="R4" t="n">
-        <v>6610578</v>
+        <v>6610593</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca 200 st på en yta av 4×4 m. Såg några här o var i området. 3 st gamla blomställningar.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,14 +1010,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1039,60 +1021,67 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jesper Granback, Petter Brorson Edh</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130123722</v>
+        <v>130124199</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnmyrbäcken, Björnmyrbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>367260</v>
+        <v>367331</v>
       </c>
       <c r="R5" t="n">
-        <v>6610593</v>
+        <v>6610578</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca 200 st på en yta av 4×4 m. Såg några här o var i området. 3 st gamla blomställningar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,8 +1134,14 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jesper Granback, Petter Brorson Edh</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 57119-2025 artfynd.xlsx
+++ b/artfynd/A 57119-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>130124803</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,60 +916,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130124199</v>
+        <v>130123722</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnmyrbäcken, Björnmyrbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>367331</v>
+        <v>367260</v>
       </c>
       <c r="R4" t="n">
-        <v>6610578</v>
+        <v>6610593</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca 200 st på en yta av 4×4 m. Såg några här o var i området. 3 st gamla blomställningar.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,14 +1010,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1039,60 +1021,67 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jesper Granback, Petter Brorson Edh</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130123722</v>
+        <v>130124199</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>98923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnmyrbäcken, Björnmyrbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>367260</v>
+        <v>367331</v>
       </c>
       <c r="R5" t="n">
-        <v>6610593</v>
+        <v>6610578</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca 200 st på en yta av 4×4 m. Såg några här o var i området. 3 st gamla blomställningar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,8 +1134,14 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jesper Granback, Petter Brorson Edh</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1161,7 +1161,7 @@
         <v>130238708</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>130238763</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57119-2025 artfynd.xlsx
+++ b/artfynd/A 57119-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>130124803</v>
       </c>
       <c r="B3" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>130123722</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>130124199</v>
       </c>
       <c r="B5" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>130238708</v>
       </c>
       <c r="B6" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>130238763</v>
       </c>
       <c r="B7" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57119-2025 artfynd.xlsx
+++ b/artfynd/A 57119-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>130238708</v>
       </c>
       <c r="B6" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>130238763</v>
       </c>
       <c r="B7" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57119-2025 artfynd.xlsx
+++ b/artfynd/A 57119-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>130238708</v>
       </c>
       <c r="B6" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>130238763</v>
       </c>
       <c r="B7" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57119-2025 artfynd.xlsx
+++ b/artfynd/A 57119-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>130238708</v>
       </c>
       <c r="B6" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>130238763</v>
       </c>
       <c r="B7" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57119-2025 artfynd.xlsx
+++ b/artfynd/A 57119-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>130238708</v>
       </c>
       <c r="B6" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>130238763</v>
       </c>
       <c r="B7" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
